--- a/reports/per_step_active_state/DETAILED_TABLE.xlsx
+++ b/reports/per_step_active_state/DETAILED_TABLE.xlsx
@@ -1450,12 +1450,12 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>498.0B</t>
+          <t>16.0B</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>1.0x</t>
+          <t>32.0x</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
@@ -1475,12 +1475,12 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>81.1KiB</t>
+          <t>4.0KiB</t>
         </is>
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>0.53x</t>
+          <t>10.7x</t>
         </is>
       </c>
     </row>
@@ -1507,12 +1507,12 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>1.4KiB</t>
+          <t>512.0B</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>2.9x</t>
+          <t>8.0x</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -1532,12 +1532,12 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>410.0KiB</t>
+          <t>53.7KiB</t>
         </is>
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>2.2x</t>
+          <t>17.2x</t>
         </is>
       </c>
     </row>
@@ -1564,12 +1564,12 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>2.1KiB</t>
+          <t>16.0B</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>61.2x</t>
+          <t>8192x</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -1589,12 +1589,12 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>1.2MiB</t>
+          <t>13.4KiB</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>27.0x</t>
+          <t>2535x</t>
         </is>
       </c>
     </row>
@@ -1621,12 +1621,12 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>135.0KiB</t>
+          <t>128.0KiB</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>1942x</t>
+          <t>2048x</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -1646,12 +1646,12 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>132.6MiB</t>
+          <t>115.1MiB</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>3401x</t>
+          <t>3917x</t>
         </is>
       </c>
     </row>
@@ -1678,12 +1678,12 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>230.0B</t>
+          <t>128.0B</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>2.2x</t>
+          <t>4.0x</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -1703,12 +1703,12 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>254.1KiB</t>
+          <t>92.3KiB</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>1.1x</t>
+          <t>3.1x</t>
         </is>
       </c>
     </row>
@@ -1735,12 +1735,12 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>416.0B</t>
+          <t>256.0B</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>0.62x</t>
+          <t>1.0x</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -1760,12 +1760,12 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>51.5KiB</t>
+          <t>22.2KiB</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>0.89x</t>
+          <t>2.1x</t>
         </is>
       </c>
     </row>
@@ -1792,12 +1792,12 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>16.2KiB</t>
+          <t>16.0KiB</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>0.99x</t>
+          <t>1.0x</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -1817,12 +1817,12 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>4.0MiB</t>
+          <t>3.5MiB</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>2.0x</t>
+          <t>2.2x</t>
         </is>
       </c>
     </row>
@@ -1849,37 +1849,37 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>0.0B</t>
+          <t>16.0B</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
+          <t>1.0x</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>43.0KiB</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
         <is>
           <t>43.0KiB</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I10" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>0.0B</t>
-        </is>
-      </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1.0x</t>
         </is>
       </c>
     </row>

--- a/reports/per_step_active_state/DETAILED_TABLE.xlsx
+++ b/reports/per_step_active_state/DETAILED_TABLE.xlsx
@@ -1450,12 +1450,12 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>16.0B</t>
+          <t>498.0B</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>32.0x</t>
+          <t>1.0x</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
@@ -1475,12 +1475,12 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>4.0KiB</t>
+          <t>81.1KiB</t>
         </is>
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>10.7x</t>
+          <t>0.53x</t>
         </is>
       </c>
     </row>
@@ -1507,12 +1507,12 @@
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t>512.0B</t>
+          <t>1.4KiB</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>8.0x</t>
+          <t>2.9x</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -1532,12 +1532,12 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>53.7KiB</t>
+          <t>410.0KiB</t>
         </is>
       </c>
       <c r="K4" s="4" t="inlineStr">
         <is>
-          <t>17.2x</t>
+          <t>2.2x</t>
         </is>
       </c>
     </row>
@@ -1564,12 +1564,12 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>16.0B</t>
+          <t>2.1KiB</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>8192x</t>
+          <t>61.2x</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
@@ -1589,12 +1589,12 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>13.4KiB</t>
+          <t>1.2MiB</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>2535x</t>
+          <t>27.0x</t>
         </is>
       </c>
     </row>
@@ -1621,12 +1621,12 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t>128.0KiB</t>
+          <t>135.0KiB</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>2048x</t>
+          <t>1942x</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
@@ -1646,12 +1646,12 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>115.1MiB</t>
+          <t>132.6MiB</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>3917x</t>
+          <t>3401x</t>
         </is>
       </c>
     </row>
@@ -1678,12 +1678,12 @@
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>128.0B</t>
+          <t>230.0B</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>4.0x</t>
+          <t>2.2x</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
@@ -1703,12 +1703,12 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>92.3KiB</t>
+          <t>254.1KiB</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>3.1x</t>
+          <t>1.1x</t>
         </is>
       </c>
     </row>
@@ -1735,12 +1735,12 @@
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t>256.0B</t>
+          <t>416.0B</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>1.0x</t>
+          <t>0.62x</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
@@ -1760,12 +1760,12 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>22.2KiB</t>
+          <t>51.5KiB</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>2.1x</t>
+          <t>0.89x</t>
         </is>
       </c>
     </row>
@@ -1792,12 +1792,12 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>16.0KiB</t>
+          <t>16.2KiB</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>1.0x</t>
+          <t>0.99x</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -1817,12 +1817,12 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>3.5MiB</t>
+          <t>4.0MiB</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>2.2x</t>
+          <t>2.0x</t>
         </is>
       </c>
     </row>
@@ -1849,12 +1849,12 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t>16.0B</t>
+          <t>0.0B</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>1.0x</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -1874,12 +1874,12 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>43.0KiB</t>
+          <t>0.0B</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>1.0x</t>
+          <t>-</t>
         </is>
       </c>
     </row>

--- a/reports/per_step_active_state/DETAILED_TABLE.xlsx
+++ b/reports/per_step_active_state/DETAILED_TABLE.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -29,13 +29,16 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <color rgb="001F7A1F"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -44,22 +47,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9E1F2"/>
+        <fgColor rgb="00305496"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00305496"/>
+        <fgColor rgb="008EA9DB"/>
       </patternFill>
     </fill>
   </fills>
@@ -89,25 +82,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,12 +460,12 @@
   <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -498,7 +481,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>NC transient 2^b</t>
+          <t>fused transient 2^b</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -508,7 +491,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>NC resident 2^b</t>
+          <t>fused resident 2^b</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -523,29 +506,29 @@
           <t>coherent_d3_r1</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>2^5</t>
         </is>
       </c>
-      <c r="C2" s="3" t="inlineStr">
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>2^1</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>16x</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>2^0</t>
         </is>
       </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>32x win</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>2^0</t>
-        </is>
-      </c>
-      <c r="F2" s="4" t="inlineStr">
-        <is>
-          <t>32x win</t>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>32x</t>
         </is>
       </c>
     </row>
@@ -555,29 +538,29 @@
           <t>coherent_d3_r3</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>2^8</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>2^5</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>8x win</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>2^4</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>16x win</t>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>16x</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>2^4</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>16x</t>
         </is>
       </c>
     </row>
@@ -587,29 +570,29 @@
           <t>coherent_d5_r1</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>2^13</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>2^1</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>4.1e+03x</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>2^0</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>8192x win</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>2^0</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>8192x win</t>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>8.19e+03x</t>
         </is>
       </c>
     </row>
@@ -619,29 +602,29 @@
           <t>coherent_d5_r5</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>2^24</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>2^13</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>2048x win</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>2^12</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>4096x win</t>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>4.1e+03x</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2^12</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>4.1e+03x</t>
         </is>
       </c>
     </row>
@@ -651,29 +634,29 @@
           <t>distillation</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>2^5</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
         <is>
           <t>2^3</t>
         </is>
       </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>4x win</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>2^2</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>8x win</t>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>4x</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2^3</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>4x</t>
         </is>
       </c>
     </row>
@@ -683,29 +666,29 @@
           <t>cultivation_d3</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>2^4</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>2^4</t>
-        </is>
-      </c>
-      <c r="D7" s="5" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>2^3</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>2x win</t>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>2x</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2^3</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>2x</t>
         </is>
       </c>
     </row>
@@ -715,29 +698,29 @@
           <t>cultivation_d5</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>2^10</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>2^10</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
         <is>
           <t>2^9</t>
         </is>
       </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>2x win</t>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>2x</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2^9</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>2x</t>
         </is>
       </c>
     </row>
@@ -747,27 +730,27 @@
           <t>surface_d7_r7</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>2^0</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
         <is>
           <t>2^0</t>
         </is>
       </c>
-      <c r="D9" s="5" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>parity</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>2^0</t>
         </is>
       </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>parity</t>
         </is>
@@ -787,29 +770,28 @@
   <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr"/>
-      <c r="B1" s="6" t="inlineStr">
-        <is>
-          <t>PEAK</t>
-        </is>
-      </c>
-      <c r="G1" s="6" t="inlineStr">
-        <is>
-          <t>SUM</t>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>PEAK (max over steps)</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>SUM (integrated over steps)</t>
         </is>
       </c>
     </row>
@@ -821,52 +803,52 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>Clifft PEAK</t>
+          <t>Clifft</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>TTN PEAK</t>
+          <t>fused transient</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
-          <t>TTN x</t>
+          <t>x</t>
         </is>
       </c>
       <c r="E2" s="1" t="inlineStr">
         <is>
-          <t>near-Clifford PEAK</t>
+          <t>fused resident</t>
         </is>
       </c>
       <c r="F2" s="1" t="inlineStr">
         <is>
-          <t>NC x</t>
+          <t>x</t>
         </is>
       </c>
       <c r="G2" s="1" t="inlineStr">
         <is>
-          <t>Clifft SUM</t>
+          <t>Clifft</t>
         </is>
       </c>
       <c r="H2" s="1" t="inlineStr">
         <is>
-          <t>TTN SUM</t>
+          <t>fused transient</t>
         </is>
       </c>
       <c r="I2" s="1" t="inlineStr">
         <is>
-          <t>TTN x</t>
+          <t>x</t>
         </is>
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>near-Clifford SUM</t>
+          <t>fused resident</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>NC x</t>
+          <t>x</t>
         </is>
       </c>
     </row>
@@ -876,52 +858,52 @@
           <t>coherent_d3_r1</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>2^5</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>2^6.19</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>0.44x</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>2^1</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>16x</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>2^0</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>32.0x</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>32x</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>2^11.42</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>2^13.22</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>0.29x</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>2^8</t>
-        </is>
-      </c>
-      <c r="K3" s="4" t="inlineStr">
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>2^8.04</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>10.4x</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>2^8.00</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>10.7x</t>
         </is>
@@ -933,54 +915,54 @@
           <t>coherent_d3_r3</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>2^8</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>2^9.48</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>0.36x</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>2^5</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>8.0x</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>2^4</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>16x</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2^4</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>16x</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>2^15.85</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>2^17.23</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr">
-        <is>
-          <t>0.38x</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>2^11.75</t>
-        </is>
-      </c>
-      <c r="K4" s="4" t="inlineStr">
-        <is>
-          <t>17.2x</t>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>2^11.69</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>17.8x</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2^11.69</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>17.9x</t>
         </is>
       </c>
     </row>
@@ -990,54 +972,54 @@
           <t>coherent_d5_r1</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>2^13</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>2^11.55</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>2.7x</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>2^1</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>4.1e+03x</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>2^0</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>8192x</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>8.19e+03x</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>2^21.05</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>2^19.67</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>2.6x</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>2^9.78</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>2.47e+03x</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>2^9.74</t>
         </is>
       </c>
-      <c r="K5" s="4" t="inlineStr">
-        <is>
-          <t>2535x</t>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>2.53e+03x</t>
         </is>
       </c>
     </row>
@@ -1047,54 +1029,54 @@
           <t>coherent_d5_r5</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>2^24</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>2^23.76</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>1.2x</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>2^13</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>2048x</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>2^12</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>4.1e+03x</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2^12</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>4.1e+03x</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>2^34.78</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>2^31.89†</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>5.5x</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>2^22.85</t>
-        </is>
-      </c>
-      <c r="K6" s="4" t="inlineStr">
-        <is>
-          <t>3917x</t>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>2^22.81</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>4.01e+03x</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>2^22.81</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>4.01e+03x</t>
         </is>
       </c>
     </row>
@@ -1104,54 +1086,54 @@
           <t>distillation</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>2^5</t>
         </is>
       </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>2^5.36</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>0.78x</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
         <is>
           <t>2^3</t>
         </is>
       </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>4.0x</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>4x</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2^3</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>4x</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>2^14.15</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>2^15.89</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="inlineStr">
-        <is>
-          <t>0.30x</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>2^12.53</t>
-        </is>
-      </c>
-      <c r="K7" s="4" t="inlineStr">
-        <is>
-          <t>3.1x</t>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2^12.80</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>2.54x</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>2^12.80</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>2.54x</t>
         </is>
       </c>
     </row>
@@ -1161,54 +1143,54 @@
           <t>cultivation_d3</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>2^4</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>2^6.21</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>0.22x</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>2^4</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>1.0x</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>2^3</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>2x</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2^3</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>2x</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>2^11.52</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>2^13.33</t>
-        </is>
-      </c>
-      <c r="I8" s="4" t="inlineStr">
-        <is>
-          <t>0.28x</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>2^10.47</t>
-        </is>
-      </c>
-      <c r="K8" s="4" t="inlineStr">
-        <is>
-          <t>2.1x</t>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>2^10.44</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>2.11x</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>2^10.44</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>2.11x</t>
         </is>
       </c>
     </row>
@@ -1218,54 +1200,54 @@
           <t>cultivation_d5</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>2^10</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>2^11.17</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>0.45x</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>2^10</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>1.0x</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>2^9</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>2x</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>2^9</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>2x</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>2^18.97</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>2^19.01</t>
-        </is>
-      </c>
-      <c r="I9" s="4" t="inlineStr">
-        <is>
-          <t>0.97x</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>2^17.80</t>
-        </is>
-      </c>
-      <c r="K9" s="4" t="inlineStr">
-        <is>
-          <t>2.2x</t>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>2^17.79</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>2.27x</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>2^17.79</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>2.27x</t>
         </is>
       </c>
     </row>
@@ -1275,60 +1257,62 @@
           <t>surface_d7_r7</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>2^0</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
         <is>
           <t>2^0</t>
         </is>
       </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>1.0x</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2^0</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>2^11.43</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I10" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>2^11.43</t>
         </is>
       </c>
-      <c r="K10" s="4" t="inlineStr">
-        <is>
-          <t>1.0x</t>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>2^11.43</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="4">
     <mergeCell ref="B1:F1"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="F1:I1"/>
     <mergeCell ref="G1:K1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1344,29 +1328,28 @@
   <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="17" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr"/>
-      <c r="B1" s="6" t="inlineStr">
-        <is>
-          <t>PEAK</t>
-        </is>
-      </c>
-      <c r="G1" s="6" t="inlineStr">
-        <is>
-          <t>SUM</t>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>PEAK (max over steps)</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>SUM (integrated over steps)</t>
         </is>
       </c>
     </row>
@@ -1378,52 +1361,52 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>Clifft PEAK</t>
+          <t>Clifft</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>TTN PEAK</t>
+          <t>fused transient</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
-          <t>TTN x</t>
+          <t>x</t>
         </is>
       </c>
       <c r="E2" s="1" t="inlineStr">
         <is>
-          <t>near-Clifford PEAK</t>
+          <t>fused resident</t>
         </is>
       </c>
       <c r="F2" s="1" t="inlineStr">
         <is>
-          <t>NC x</t>
+          <t>x</t>
         </is>
       </c>
       <c r="G2" s="1" t="inlineStr">
         <is>
-          <t>Clifft SUM</t>
+          <t>Clifft</t>
         </is>
       </c>
       <c r="H2" s="1" t="inlineStr">
         <is>
-          <t>TTN SUM</t>
+          <t>fused transient</t>
         </is>
       </c>
       <c r="I2" s="1" t="inlineStr">
         <is>
-          <t>TTN x</t>
+          <t>x</t>
         </is>
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>near-Clifford SUM</t>
+          <t>fused resident</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>NC x</t>
+          <t>x</t>
         </is>
       </c>
     </row>
@@ -1433,54 +1416,54 @@
           <t>coherent_d3_r1</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t>512.0B</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>1.1KiB</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>0.44x</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>498.0B</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>1.0x</t>
-        </is>
-      </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>512B</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>32B</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>16x</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>16B</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>32x</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>42.8KiB</t>
         </is>
       </c>
-      <c r="H3" s="3" t="inlineStr">
-        <is>
-          <t>149.4KiB</t>
-        </is>
-      </c>
-      <c r="I3" s="4" t="inlineStr">
-        <is>
-          <t>0.29x</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>81.1KiB</t>
-        </is>
-      </c>
-      <c r="K3" s="4" t="inlineStr">
-        <is>
-          <t>0.53x</t>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>4.1KiB</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>10.4x</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>4.0KiB</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>10.7x</t>
         </is>
       </c>
     </row>
@@ -1490,54 +1473,54 @@
           <t>coherent_d3_r3</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>4.0KiB</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>11.1KiB</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="inlineStr">
-        <is>
-          <t>0.36x</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>1.4KiB</t>
-        </is>
-      </c>
-      <c r="F4" s="4" t="inlineStr">
-        <is>
-          <t>2.9x</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>256B</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>16x</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>256B</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>16x</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>922.0KiB</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>2.3MiB</t>
-        </is>
-      </c>
-      <c r="I4" s="4" t="inlineStr">
-        <is>
-          <t>0.38x</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>410.0KiB</t>
-        </is>
-      </c>
-      <c r="K4" s="4" t="inlineStr">
-        <is>
-          <t>2.2x</t>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>51.7KiB</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>17.8x</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>51.6KiB</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>17.9x</t>
         </is>
       </c>
     </row>
@@ -1547,54 +1530,54 @@
           <t>coherent_d5_r1</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>128.0KiB</t>
         </is>
       </c>
-      <c r="C5" s="3" t="inlineStr">
-        <is>
-          <t>46.8KiB</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>2.7x</t>
-        </is>
-      </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>2.1KiB</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
-          <t>61.2x</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>32B</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>4.1e+03x</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>16B</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t>8.19e+03x</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>33.2MiB</t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t>12.8MiB</t>
-        </is>
-      </c>
-      <c r="I5" s="4" t="inlineStr">
-        <is>
-          <t>2.6x</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>1.2MiB</t>
-        </is>
-      </c>
-      <c r="K5" s="4" t="inlineStr">
-        <is>
-          <t>27.0x</t>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>13.8KiB</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>2.47e+03x</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>13.4KiB</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>2.53e+03x</t>
         </is>
       </c>
     </row>
@@ -1604,54 +1587,54 @@
           <t>coherent_d5_r5</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>256.0MiB</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>217.3MiB</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="inlineStr">
-        <is>
-          <t>1.2x</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>135.0KiB</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
-          <t>1942x</t>
-        </is>
-      </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>64.0KiB</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>4.1e+03x</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>64.0KiB</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>4.1e+03x</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>440.4GiB</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>59.4GiB†</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>5.5x</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>132.6MiB</t>
-        </is>
-      </c>
-      <c r="K6" s="4" t="inlineStr">
-        <is>
-          <t>3401x</t>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>112.5MiB</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>4.01e+03x</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>112.5MiB</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>4.01e+03x</t>
         </is>
       </c>
     </row>
@@ -1661,54 +1644,54 @@
           <t>distillation</t>
         </is>
       </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>512.0B</t>
-        </is>
-      </c>
-      <c r="C7" s="3" t="inlineStr">
-        <is>
-          <t>656.0B</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>0.78x</t>
-        </is>
-      </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>230.0B</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>2.2x</t>
-        </is>
-      </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>512B</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>128B</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>4x</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>128B</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
+        <is>
+          <t>4x</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>283.1KiB</t>
         </is>
       </c>
-      <c r="H7" s="3" t="inlineStr">
-        <is>
-          <t>946.9KiB</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="inlineStr">
-        <is>
-          <t>0.30x</t>
-        </is>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>254.1KiB</t>
-        </is>
-      </c>
-      <c r="K7" s="4" t="inlineStr">
-        <is>
-          <t>1.1x</t>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>111.2KiB</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>2.54x</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>111.2KiB</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>2.54x</t>
         </is>
       </c>
     </row>
@@ -1718,54 +1701,54 @@
           <t>cultivation_d3</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>256.0B</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>1.2KiB</t>
-        </is>
-      </c>
-      <c r="D8" s="4" t="inlineStr">
-        <is>
-          <t>0.22x</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>416.0B</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
-          <t>0.62x</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>256B</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>128B</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>2x</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>128B</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>2x</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>45.9KiB</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>161.1KiB</t>
-        </is>
-      </c>
-      <c r="I8" s="4" t="inlineStr">
-        <is>
-          <t>0.28x</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>51.5KiB</t>
-        </is>
-      </c>
-      <c r="K8" s="4" t="inlineStr">
-        <is>
-          <t>0.89x</t>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>21.7KiB</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>2.11x</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>21.7KiB</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>2.11x</t>
         </is>
       </c>
     </row>
@@ -1775,54 +1758,54 @@
           <t>cultivation_d5</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>16.0KiB</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>35.9KiB</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>0.45x</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>16.2KiB</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>0.99x</t>
-        </is>
-      </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>8.0KiB</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>2x</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>8.0KiB</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>2x</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>7.8MiB</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr">
-        <is>
-          <t>8.1MiB</t>
-        </is>
-      </c>
-      <c r="I9" s="4" t="inlineStr">
-        <is>
-          <t>0.97x</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>4.0MiB</t>
-        </is>
-      </c>
-      <c r="K9" s="4" t="inlineStr">
-        <is>
-          <t>2.0x</t>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>3.5MiB</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>2.27x</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>3.5MiB</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>2.27x</t>
         </is>
       </c>
     </row>
@@ -1832,60 +1815,62 @@
           <t>surface_d7_r7</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>16.0B</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D10" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>0.0B</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>16B</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>16B</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>16B</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>43.0KiB</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I10" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>0.0B</t>
-        </is>
-      </c>
-      <c r="K10" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>43.0KiB</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>43.0KiB</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="4">
     <mergeCell ref="B1:F1"/>
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="F1:I1"/>
     <mergeCell ref="G1:K1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
